--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_weight_contract_sensitivity.xlsx
@@ -553,7 +553,7 @@
         <v>0.5294117647058824</v>
       </c>
       <c r="H2">
-        <v>0.9428571428571428</v>
+        <v>0.8637362637362638</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.01411589895988113</v>
+        <v>0.0145873320537428</v>
       </c>
       <c r="H3">
-        <v>0.9780219780219781</v>
+        <v>0.9340659340659341</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
@@ -653,16 +653,16 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>4.974752009421024</v>
+        <v>4.98653584807848</v>
       </c>
       <c r="F2">
-        <v>4.964634239289306</v>
+        <v>4.975188110774293</v>
       </c>
       <c r="G2">
-        <v>4.959896907889774</v>
+        <v>4.973780037039223</v>
       </c>
       <c r="H2">
-        <v>-0.01011777013171912</v>
+        <v>-0.01134773730418753</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -688,16 +688,16 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>4.954886872916855</v>
+        <v>4.982720215290163</v>
       </c>
       <c r="F3">
-        <v>4.93178496289583</v>
+        <v>4.95739729486909</v>
       </c>
       <c r="G3">
-        <v>4.923660234259316</v>
+        <v>4.957100693775069</v>
       </c>
       <c r="H3">
-        <v>-0.02310191002102519</v>
+        <v>-0.02532292042107295</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -793,16 +793,16 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>4.942114530052909</v>
+        <v>4.969067271191751</v>
       </c>
       <c r="F6">
-        <v>4.93648979343922</v>
+        <v>4.963148323147151</v>
       </c>
       <c r="G6">
-        <v>4.922213613076152</v>
+        <v>4.956476038819342</v>
       </c>
       <c r="H6">
-        <v>-0.005624736613689755</v>
+        <v>-0.005918948044599619</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -828,16 +828,16 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>4.958148899063696</v>
+        <v>4.975729121357084</v>
       </c>
       <c r="F7">
-        <v>4.956801614236591</v>
+        <v>4.974403147919012</v>
       </c>
       <c r="G7">
-        <v>4.945344444591945</v>
+        <v>4.967909225760259</v>
       </c>
       <c r="H7">
-        <v>-0.0013472848271048</v>
+        <v>-0.001325973438071887</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:11">
